--- a/docs/attorney/LexVerify_Test_Cases.xlsx
+++ b/docs/attorney/LexVerify_Test_Cases.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Priority Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$M$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$M$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -941,16 +941,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>41</v>
@@ -967,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3226,15 +3226,19 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -4263,15 +4267,19 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4559,15 +4567,19 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -4618,15 +4630,19 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -4749,43 +4765,43 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>TEAM-001</t>
+          <t>DSH-005</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Firm Team &amp; Staff Invitations</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Team page lists firm members</t>
+          <t>Dashboard shows no fabricated data</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Logged in as Firm Admin</t>
+          <t>New firm with no cases/hearings</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>1. Open Team page</t>
+          <t>1. Open /dashboard</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Members listed with name, email, role, status; search box 'Search team members'.</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Greeting/summary reflects real data; no hardcoded 'priority hearings this week'.</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -4795,148 +4811,156 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>BUG: brand-new firm with no cases shows 'You have 3 priority hearings this week' (hardcoded).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>TEAM-001</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Firm Team &amp; Staff Invitations</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Team page lists firm members</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Logged in as Firm Admin</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>1. Open Team page</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Members listed with name, email, role, status; search box 'Search team members'.</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
           <t>TEAM-002</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Invite an Attorney</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Firm Admin on Team page</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>1. Click 'Add Team Member'
 2. Choose Attorney, enter email
 3. Send Invitation</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>New email</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>Invitation created as pending; email sent.</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>TEAM-003</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>Firm Team &amp; Staff Invitations</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Invite a Paralegal</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin on Team page</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>1. Add Team Member → Paralegal → Send</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>New email</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Pending paralegal invitation created.</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TEAM-004</t>
+          <t>TEAM-003</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -4946,23 +4970,27 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Invalid / empty invite email</t>
+          <t>Invite a Paralegal</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Invite dialog open</t>
+          <t>Firm Admin on Team page</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>1. Submit with empty or invalid email</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr"/>
+          <t>1. Add Team Member → Paralegal → Send</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>New email</t>
+        </is>
+      </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Validation error; no invitation created.</t>
+          <t>Pending paralegal invitation created.</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -4972,7 +5000,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -4982,20 +5010,24 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>TEAM-005</t>
+          <t>TEAM-004</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -5005,23 +5037,23 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Attorney/Paralegal cannot invite staff</t>
+          <t>Invalid / empty invite email</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Logged in as Attorney</t>
+          <t>Invite dialog open</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>1. Open Team page / call invite API</t>
+          <t>1. Submit with empty or invalid email</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>No 'Add Team Member' control; API returns 403.</t>
+          <t>Validation error; no invitation created.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -5031,30 +5063,34 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Firm Admin</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TEAM-006</t>
+          <t>TEAM-005</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -5064,38 +5100,38 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Search team members</t>
+          <t>Attorney/Paralegal cannot invite staff</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Several members</t>
+          <t>Logged in as Attorney</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>1. Type part of a name/email in search</t>
+          <t>1. Open Team page / call invite API</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>List filters to matching members.</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>No 'Add Team Member' control; API returns 403.</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -5113,7 +5149,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>TEAM-007</t>
+          <t>TEAM-006</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -5123,28 +5159,28 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Resend pending invitation (inviter only)</t>
+          <t>Search team members</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Pending invitation sent by me</t>
+          <t>Several members</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>1. Resend</t>
+          <t>1. Type part of a name/email in search</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>New link emailed; old link invalid.</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>List filters to matching members.</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
@@ -5159,7 +5195,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Needs mailbox</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -5172,93 +5208,93 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
+          <t>TEAM-007</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Firm Team &amp; Staff Invitations</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Resend pending invitation (inviter only)</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Pending invitation sent by me</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>1. Resend</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>New link emailed; old link invalid.</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Needs mailbox</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
           <t>TEAM-008</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Revoke pending invitation (inviter only)</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Pending invitation sent by me</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>1. Revoke
 2. Open the old link</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Invitation revoked; link shows it is no longer valid.</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>Needs mailbox</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>TEAM-009</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Firm Team &amp; Staff Invitations</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Non-inviter cannot revoke</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Invitation sent by another user</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>1. Try to revoke it</t>
-        </is>
-      </c>
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Action not allowed (documented policy: inviter only).</t>
+          <t>Invitation revoked; link shows it is no longer valid.</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -5268,7 +5304,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
@@ -5278,7 +5314,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
+          <t>Needs mailbox</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -5291,7 +5327,7 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TEAM-010</t>
+          <t>TEAM-009</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -5301,23 +5337,23 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Duplicate invite to existing member</t>
+          <t>Non-inviter cannot revoke</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Email already in firm</t>
+          <t>Invitation sent by another user</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>1. Invite the same email again</t>
+          <t>1. Try to revoke it</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Clear error; no duplicate membership.</t>
+          <t>Action not allowed (documented policy: inviter only).</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5327,7 +5363,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -5350,38 +5386,38 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>INV-001</t>
+          <t>TEAM-010</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Invitation Accept</t>
+          <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Accept page without token</t>
+          <t>Duplicate invite to existing member</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Email already in firm</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>1. Open http://34.232.246.13:3000/invite/accept</t>
+          <t>1. Invite the same email again</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Error 'No invitation token provided'.</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Clear error; no duplicate membership.</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -5391,70 +5427,66 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Firm Admin</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="M72" s="5" t="inlineStr">
-        <is>
-          <t>Automated — passed (2/2 runs)</t>
-        </is>
-      </c>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>INV-002</t>
+          <t>TEAM-011</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Invitation Accept</t>
+          <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Invalid token</t>
+          <t>Team page header shows the signed-in user</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Logged in as Firm Admin</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>1. Open http://34.232.246.13:3000/invite/accept?token=invalid123</t>
+          <t>1. Open Team page</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Error 'Invalid invitation link'.</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Header shows the signed-in user's name/role; no placeholder user; filters list real offices/departments.</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Firm Admin</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
@@ -5462,98 +5494,415 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Automated — passed (2/2 runs)</t>
+          <t>BUG: Team page header shows placeholder 'Sarah Jenkins, Senior Associate'; office filter lists mock values (New York HQ, London, Munich…).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>INV-003</t>
+          <t>TEAM-012</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Invitation Accept</t>
+          <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Used or expired token</t>
+          <t>Firm Admin appears in the firm member list</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Token already accepted</t>
+          <t>Logged in as Firm Admin</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>1. Open the used link</t>
+          <t>1. Open Team page</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>'This invitation has already been used or has expired'.</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>The Firm Admin's own membership is listed.</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Invitee</t>
+          <t>Firm Admin</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>Needs mailbox</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M74" s="5" t="inlineStr"/>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>BUG (observed): Firm Admin is not listed — 'Showing 0-0 of 0 members'.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
+          <t>TEAM-013</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Firm Team &amp; Staff Invitations</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Invite success screen gives a usable invite link</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>1. Invite an Attorney
+2. Read 'Unique Invite Link'</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Link carries a real token (…/invite/accept?token=&lt;token&gt;) and the Invitation Token ID is filled.</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>BUG: after inviting an Attorney, 'Unique Invite Link' is …/invite/accept?token=null and 'Invitation Token ID' is empty — the link can't be used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>TEAM-014</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Firm Team &amp; Staff Invitations</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Invite success screen shows the chosen role</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>1. Invite an Attorney
+2. Read 'Access Role'</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Access Role shows 'Attorney' (or 'Paralegal') as chosen.</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>BUG: invited as Attorney/Paralegal, but the success screen shows Access Role 'Standard User'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>INV-001</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Invitation Accept</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Accept page without token</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>1. Open http://34.232.246.13:3000/invite/accept</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Error 'No invitation token provided'.</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (2/2 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>INV-002</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Invitation Accept</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Invalid token</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>1. Open http://34.232.246.13:3000/invite/accept?token=invalid123</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Error 'Invalid invitation link'.</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (2/2 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>INV-003</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Invitation Accept</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Used or expired token</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Token already accepted</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the used link</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>'This invitation has already been used or has expired'.</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Invitee</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Needs mailbox</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
           <t>INV-004</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>New user accepts via sign-up</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Valid token, email not registered</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>1. Open link
 2. Sign up (email locked)
@@ -5561,1271 +5910,1004 @@
 4. Accept</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>Account created, invitation accepted, lands in the right workspace.</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Invitee</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>INV-005</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Existing user accepts after login</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Valid token, account exists</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>1. Open link while signed out
 2. Log in
 3. Accept Invitation</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Token preserved through login; after accept user is added (staff → firm, client → case).</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Invitee</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>INV-006</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Wrong account logged in</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Logged in as a different email</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>1. Open invitation link</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>'Wrong account' warning telling the user to switch to the invited email.</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Invitee</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>INV-007</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>First accepted client invite activates draft case</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Draft case with pending client invite</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>1. Client accepts</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>Case status changes draft → active.</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>Beneficiary</t>
         </is>
       </c>
-      <c r="K78" s="5" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>INV-008</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>Firm staff cannot be invited as client on own firm case</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Existing paralegal email</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>1. Invite that email as beneficiary on firm case</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Blocked with 'internal staff cannot also be a client' (known gap on some paths — record result).</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>INV-009</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>Self-petition: same email as beneficiary and petitioner</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Draft case</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>1. Invite same email for both roles
 2. Accept</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Both invitations accepted; person listed twice with both roles (expected).</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H85" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>INV-010</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>Invitation Accept</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>Token can be used only once</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Accepted token</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>1. Accept again in another browser</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>Second attempt rejected.</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Invitee</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>CASE-001</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Create case page layout</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>1. Open /cases/new</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>'Create a new case', Case name field (placeholder 'Doe — EB-1A Petition'), Case type dropdown ('Select a case type…'), submit button.</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>CASE-002</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>Case name required</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>On /cases/new</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>1. Leave name empty
 2. Submit</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Error 'Case name is required.'</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>CASE-003</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>Case type required</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>On /cases/new</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>1. Enter name, no type
 2. Submit</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>Error 'Case type is required.'</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>CASE-004</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Case types are loaded</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>On /cases/new</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>1. Open the Case type dropdown</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Seeded types listed (I-129 H-1B, I-485 AOS).</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>CASE-005</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>Create case successfully</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>On /cases/new</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>1. Enter name + type
 2. Submit</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>Auto QA – H-1B &lt;timestamp&gt;</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>Redirected to /cases/&lt;id&gt;/team; case is in draft; 'This case has no team yet…' shown.</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>CASE-006</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Whitespace-only case name</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>On /cases/new</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>1. Enter '   ' as name
 2. Submit</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>Error 'Case name is required.'</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="H92" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>CASE-007</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>Attorney/Paralegal cannot create case</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Logged in as Attorney</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>1. Open /cases/new / call create API</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>Blocked (403 / no button).</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>Attorney</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>CASE-008</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Case list shows firm cases with status</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Firm with cases</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>1. Open /cases</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>Cases listed with name, type, status (draft/active), missing-documents badge.</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>CASE-009</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Case detail page</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Existing case</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>1. Open /cases/&lt;id&gt;</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>Case overview with tabs/links to Team, Questionnaires, Documents, Tasks; created date.</t>
         </is>
       </c>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>CASE-010</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>Case Management</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Edit case name / type (Firm Admin only)</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Existing case</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>1. Edit name
 2. Save</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Change persisted; attorney/paralegal cannot edit.</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L91" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>CASE-011</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Case Management</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Soft-delete case (Firm Admin only)</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Existing test case</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>1. Delete case</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Case removed from list; others cannot delete.</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>CASE-012</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Case Management</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Attorney sees only assigned cases' details</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Attorney assigned to case A only</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>1. Open case B URL directly</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Access denied for unassigned case.</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>CASE-013</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>Case Management</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Client sees only own case</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary of case A</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/&lt;B id&gt;</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Access denied.</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>CASE-014</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Case Management</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Non-existent case id</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Logged in</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/999999</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>'Case not found.' / 404 message, no crash.</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>CTM-001</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>Case Team</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Empty draft case team message</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>New draft case</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/&lt;id&gt;/team</t>
-        </is>
-      </c>
       <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>'This case has no team yet. Add at least one beneficiary or petitioner…' shown.</t>
-        </is>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Change persisted; attorney/paralegal cannot edit.</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -6848,1167 +6930,1204 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
+          <t>CASE-011</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Case Management</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Soft-delete case (Firm Admin only)</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Existing test case</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete case</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Case removed from list; others cannot delete.</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>CASE-012</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Case Management</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Attorney sees only assigned cases' details</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Attorney assigned to case A only</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>1. Open case B URL directly</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Access denied for unassigned case.</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>CASE-013</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Case Management</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Client sees only own case</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary of case A</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /cases/&lt;B id&gt;</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Access denied.</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>CASE-014</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Case Management</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Non-existent case id</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Logged in</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /cases/999999</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>'Case not found.' / 404 message, no crash.</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>CASE-015</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Case Management</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Case detail shows no developer text</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Any case</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /cases/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>No 'TODO (product)…' or other developer notes on the page.</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>BUG: case detail shows developer text 'TODO (product): add a per-case due_at…'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>CTM-001</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Case Team</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Empty draft case team message</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>New draft case</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /cases/&lt;id&gt;/team</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>'This case has no team yet. Add at least one beneficiary or petitioner…' shown.</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t>CTM-002</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Invite beneficiary to case</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Draft case</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>1. Add invitee → Beneficiary, email, optional names
 2. Send</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>New email</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>Pending row in team table (Name, Email, Role, Status).</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>CTM-003</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>Invite petitioner to case</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>Draft case</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E104" s="5" t="inlineStr">
         <is>
           <t>1. Add invitee → Petitioner → Send</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr"/>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>Pending petitioner row.</t>
         </is>
       </c>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="H104" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I104" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M98" s="5" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>CTM-004</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>Invalid invitee email</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Case team page</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>1. Enter invalid email
 2. Send</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F105" s="5" t="inlineStr">
         <is>
           <t>invitee@</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>Validation error; nothing created.</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H105" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="J105" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed. Note: the browser's native email check fires first; the app's own message ('Invalid email: …') only shows with native validation off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>CTM-005</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Case Team</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Assign existing firm member (attorney/paralegal)</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Firm has attorney</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>1. 'Assign existing firm member' → choose → assign</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Member appears on case team with access.</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>CTM-005</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>CTM-006</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Assign existing firm member (attorney/paralegal)</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Firm has attorney</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>1. 'Assign existing firm member' → choose → assign</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Member appears on case team with access.</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>New (non-firm) attorney cannot be added directly to a case</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Email not in firm</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to add as attorney on case</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Blocked; must join firm first.</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>CTM-007</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Case Team</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Attorney on case can invite client</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Attorney assigned to case</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>1. Invite beneficiary</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Allowed (own case only).</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>CTM-006</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>CTM-008</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>New (non-firm) attorney cannot be added directly to a case</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>Email not in firm</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>1. Try to add as attorney on case</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr"/>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>Blocked; must join firm first.</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M101" s="5" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>CTM-007</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Case Team</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Attorney on case can invite client</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>Attorney assigned to case</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>1. Invite beneficiary</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>Allowed (own case only).</t>
-        </is>
-      </c>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M102" s="5" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>CTM-008</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Case Team</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>Only Firm Admin can remove team member</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Case with members</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>1. Remove as Firm Admin
 2. Try as Attorney</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>Firm Admin succeeds; attorney blocked.</t>
         </is>
       </c>
-      <c r="H103" s="9" t="inlineStr">
+      <c r="H109" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I109" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J103" s="5" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr">
+      <c r="K109" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>CTM-009</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>Case status flips to active after first acceptance</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>Pending client invite</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>1. Client accepts
 2. Reload team page</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>Status 'active'; member row 'accepted'.</t>
         </is>
       </c>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H110" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I110" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="J104" s="5" t="inlineStr">
+      <c r="J110" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K104" s="5" t="inlineStr">
+      <c r="K110" s="5" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M104" s="5" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>CTM-010</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Case Team</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Pending invitee listed on case team page</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Invite sent, not yet accepted</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>1. Invite a beneficiary
+2. Reload /cases/&lt;id&gt;/team</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Invitee row with status 'pending' and a Resend action (page says 'Firm admins can resend pending invitations').</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>BUG: invite succeeds ('Invitation sent to …'), but the invitee never appears on the team page — table stays 'No team members yet', so there is nothing to resend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>QNR-001</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>Questionnaires</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>Questionnaires tab with 'Add questionnaire'</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Case with active client</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E112" s="5" t="inlineStr">
         <is>
           <t>1. Open /cases/&lt;id&gt;/questionnaires</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>List + 'Add questionnaire' button.</t>
         </is>
       </c>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="H112" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="J105" s="5" t="inlineStr">
+      <c r="J112" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K105" s="5" t="inlineStr">
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>QNR-002</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Add questionnaire needs active beneficiary/petitioner</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Draft case, no accepted client</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>1. Click 'Add questionnaire'</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Message 'This case has no active beneficiary or petitioner yet…'; cannot attach.</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (firm-admin.spec.ts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>QNR-003</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Attach published template to case</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Active client on case</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>1. Add questionnaire → template (I-129 / I-485) → 'Filled by' role → confirm</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaire attached and listed.</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M105" s="5" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>QNR-002</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>QNR-004</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>Questionnaires</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Add questionnaire needs active beneficiary/petitioner</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>Draft case, no accepted client</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>1. Click 'Add questionnaire'</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Message 'This case has no active beneficiary or petitioner yet…'; cannot attach.</t>
-        </is>
-      </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal cannot attach questionnaire</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal on case</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>1. Try Add questionnaire</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Not allowed.</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M106" s="5" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>QNR-003</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>QNR-005</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>Questionnaires</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Attach published template to case</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>Active client on case</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>1. Add questionnaire → template (I-129 / I-485) → 'Filled by' role → confirm</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaire attached and listed.</t>
-        </is>
-      </c>
-      <c r="H107" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>QNR-004</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal cannot attach questionnaire</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal on case</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>1. Try Add questionnaire</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr"/>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>Not allowed.</t>
-        </is>
-      </c>
-      <c r="H108" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>QNR-005</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>Client fills and autosaves answers</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Questionnaire sent to client</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>1. Client answers fields
 2. Reload</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr"/>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Answers persisted (autosave / resume).</t>
-        </is>
-      </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>QNR-006</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Conditional questions show/hide</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Section with conditional rules</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>1. Toggle a controlling answer</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr"/>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Dependent questions appear/disappear per rules.</t>
-        </is>
-      </c>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>QNR-007</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Repeatable group add/remove</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>Section with repeatable group</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>1. Add and remove entries</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr"/>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>Entries added/removed and saved correctly.</t>
-        </is>
-      </c>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M111" s="5" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>QNR-008</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>Client submits questionnaire</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>All required answers filled</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>1. Submit</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr"/>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Status → submitted; client can no longer edit unless changes requested.</t>
-        </is>
-      </c>
-      <c r="H112" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="J112" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M112" s="5" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>QNR-009</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Submit with missing required answers</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>Required fields empty</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>1. Submit</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Submission gated with clear message listing missing items.</t>
-        </is>
-      </c>
-      <c r="H113" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J113" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L113" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M113" s="5" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>QNR-010</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>Attorney requests changes</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>Submitted questionnaire</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>1. Request changes with comment</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Status → changes requested; client can edit again.</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M114" s="5" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>QNR-011</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Attorney approves</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>Submitted questionnaire</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>Status → approved.</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J115" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M115" s="5" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>QNR-012</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal cannot approve / export / archive</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal on case</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>1. Look for Approve, Export PDF, Archive</t>
-        </is>
-      </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Actions not available; API 403.</t>
+          <t>Answers persisted (autosave / resume).</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -8018,12 +8137,12 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Paralegal</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -8041,7 +8160,7 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>QNR-013</t>
+          <t>QNR-006</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -8051,23 +8170,23 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Export approved questionnaire as PDF</t>
+          <t>Conditional questions show/hide</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Approved questionnaire</t>
+          <t>Section with conditional rules</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>1. Export PDF</t>
+          <t>1. Toggle a controlling answer</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr"/>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>PDF downloads with the answers (feature-flagged).</t>
+          <t>Dependent questions appear/disappear per rules.</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr">
@@ -8082,7 +8201,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Attorney</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -8100,451 +8219,447 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t>QNR-007</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Repeatable group add/remove</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Section with repeatable group</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>1. Add and remove entries</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Entries added/removed and saved correctly.</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>QNR-008</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Client submits questionnaire</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>All required answers filled</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Status → submitted; client can no longer edit unless changes requested.</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>QNR-009</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Submit with missing required answers</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Required fields empty</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Submission gated with clear message listing missing items.</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>QNR-010</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Attorney requests changes</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Submitted questionnaire</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>1. Request changes with comment</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Status → changes requested; client can edit again.</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>QNR-011</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Attorney approves</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Submitted questionnaire</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Status → approved.</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>QNR-012</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal cannot approve / export / archive</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal on case</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>1. Look for Approve, Export PDF, Archive</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Actions not available; API 403.</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>QNR-013</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Export approved questionnaire as PDF</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Approved questionnaire</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>1. Export PDF</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>PDF downloads with the answers (feature-flagged).</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Attorney</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>QNR-014</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>Questionnaires</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>Client-visible vs internal comments</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Questionnaire open</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>1. Staff adds internal and client-visible comments
 2. View as client</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr"/>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>Client sees only client-visible comments.</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L118" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M118" s="5" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>QNR-015</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>Questionnaires</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>Manual reminder to recipient</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>Pending recipient</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>1. Send reminder</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr"/>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Reminder sent; clients cannot send reminders.</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L119" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M119" s="5" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>DOC-001</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Documents page gated until questionnaire exists</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Case without questionnaire</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/&lt;id&gt;/documents</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>'Questionnaire required before document collection' with 'Back to Case Overview'.</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>DOC-002</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Required documents checklist</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>Case with questionnaire</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>1. Open Documents</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>Checklist of required documents with green/yellow/red status pills.</t>
-        </is>
-      </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>Firm Admin</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M121" s="5" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>DOC-003</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Upload valid PDF</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>Documents page</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>1. Upload a document → category → PDF &lt; 25 MB</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>sample.pdf</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Upload succeeds; checklist updates.</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M122" s="5" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>DOC-004</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Upload JPEG / PNG</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>Documents page</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>1. Upload .jpg and .png</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr"/>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>Both accepted.</t>
-        </is>
-      </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>DOC-005</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Reject unsupported file type</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>Upload modal open</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>1. Choose .docx / .exe / .txt</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr"/>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Rejected; only 'PDF, JPEG, or PNG'.</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M124" s="5" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>DOC-006</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>Reject file over 25 MB</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>Upload modal open</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>1. Choose a 26 MB PDF</t>
-        </is>
-      </c>
       <c r="F125" s="5" t="inlineStr"/>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>'File exceeds the 25 MB limit.'; upload disabled.</t>
+          <t>Client sees only client-visible comments.</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -8554,12 +8669,12 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Beneficiary</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -8577,33 +8692,33 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>DOC-007</t>
+          <t>QNR-015</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Questionnaires</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Staff upload on behalf of client</t>
+          <t>Manual reminder to recipient</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Firm staff on case</t>
+          <t>Pending recipient</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>1. Upload with 'on behalf' toggle</t>
+          <t>1. Send reminder</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Document stored with upload source attorney_on_behalf; toggle hidden for clients.</t>
+          <t>Reminder sent; clients cannot send reminders.</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
@@ -8636,7 +8751,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>DOC-008</t>
+          <t>DOC-001</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -8646,33 +8761,33 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Download document</t>
+          <t>Documents page gated until questionnaire exists</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Uploaded document</t>
+          <t>Case without questionnaire</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>1. Download</t>
+          <t>1. Open /cases/&lt;id&gt;/documents</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>Original file downloads intact.</t>
-        </is>
-      </c>
-      <c r="H127" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>'Questionnaire required before document collection' with 'Back to Case Overview'.</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -8682,20 +8797,24 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M127" s="5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed. Minor: breadcrumb shows 'Case #&lt;id&gt;' instead of the case name.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>DOC-009</t>
+          <t>DOC-002</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -8705,33 +8824,33 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Soft-delete document</t>
+          <t>Required documents checklist</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Uploaded document</t>
+          <t>Case with questionnaire</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>1. Delete</t>
+          <t>1. Open Documents</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>Removed from list; checklist recalculated.</t>
-        </is>
-      </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Checklist of required documents with green/yellow/red status pills.</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -8754,7 +8873,7 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DOC-010</t>
+          <t>DOC-003</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -8764,23 +8883,27 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Client cannot see other cases' documents</t>
+          <t>Upload valid PDF</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Two cases</t>
+          <t>Documents page</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>1. Client opens other case docs URL</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr"/>
+          <t>1. Upload a document → category → PDF &lt; 25 MB</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>sample.pdf</t>
+        </is>
+      </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>Access denied.</t>
+          <t>Upload succeeds; checklist updates.</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -8790,7 +8913,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -8813,7 +8936,7 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>DOC-011</t>
+          <t>DOC-004</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -8823,38 +8946,38 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Missing-documents badge on case list</t>
+          <t>Upload JPEG / PNG</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Case with missing required docs</t>
+          <t>Documents page</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>1. Open /cases</t>
+          <t>1. Upload .jpg and .png</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Badge shows missing count.</t>
-        </is>
-      </c>
-      <c r="H130" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Both accepted.</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -8872,48 +8995,48 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>DOC-005</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>AI Read-In (Extraction)</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Upload triggers AI extraction</t>
+          <t>Reject unsupported file type</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Upload with AI enabled</t>
+          <t>Upload modal open</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>1. Upload passport PDF</t>
+          <t>1. Choose .docx / .exe / .txt</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Extraction runs; banner shows AI suggestions awaiting review.</t>
-        </is>
-      </c>
-      <c r="H131" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Rejected; only 'PDF, JPEG, or PNG'.</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
@@ -8931,512 +9054,512 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
+          <t>DOC-006</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Reject file over 25 MB</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Upload modal open</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>1. Choose a 26 MB PDF</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>'File exceeds the 25 MB limit.'; upload disabled.</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>DOC-007</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Staff upload on behalf of client</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Firm staff on case</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload with 'on behalf' toggle</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Document stored with upload source attorney_on_behalf; toggle hidden for clients.</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Paralegal</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>DOC-008</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Download document</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Uploaded document</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>1. Download</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Original file downloads intact.</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>DOC-009</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Soft-delete document</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Uploaded document</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Removed from list; checklist recalculated.</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>DOC-010</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Client cannot see other cases' documents</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Two cases</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>1. Client opens other case docs URL</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Access denied.</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>DOC-011</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Missing-documents badge on case list</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Case with missing required docs</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /cases</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Badge shows missing count.</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>AI-001</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>AI Read-In (Extraction)</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Upload triggers AI extraction</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Upload with AI enabled</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload passport PDF</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Extraction runs; banner shows AI suggestions awaiting review.</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
           <t>AI-002</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>AI Read-In (Extraction)</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>'Disable AI run' skips extraction</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Upload modal</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>1. Tick disable AI
 2. Upload</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>No extraction created.</t>
         </is>
       </c>
-      <c r="H132" s="9" t="inlineStr">
+      <c r="H139" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
+      <c r="J139" s="5" t="inlineStr">
         <is>
           <t>Firm Admin</t>
         </is>
       </c>
-      <c r="K132" s="5" t="inlineStr">
+      <c r="K139" s="5" t="inlineStr">
         <is>
           <t>Needs account</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>AI-003</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>AI Read-In (Extraction)</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>Review page approve/edit/reject fields</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>Completed extraction</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>1. Open extract review
 2. Decide per field</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>Decisions recorded; source highlight shown.</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M133" s="5" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>AI-004</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>AI Read-In (Extraction)</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal cannot 'Confirm Approved Edits'</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal on case</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>1. Try confirm</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>Blocked (403).</t>
-        </is>
-      </c>
-      <c r="H134" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t>Paralegal</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>AI-005</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>AI Read-In (Extraction)</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>Clients cannot access extraction</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>1. Open extraction URL</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>403.</t>
-        </is>
-      </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>Beneficiary</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L135" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>TSK-001</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>Tasks</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>Case tasks page for staff</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Staff on case</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/&lt;id&gt;/tasks</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>Task list with due dates and status; open-task badge in navigation.</t>
-        </is>
-      </c>
-      <c r="H136" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K136" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>TSK-002</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>Tasks</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>Create task</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>Staff on case</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>1. Create task with title, description, due date, assignee</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr"/>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>Task listed as pending.</t>
-        </is>
-      </c>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L137" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M137" s="5" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>TSK-003</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>Tasks</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>Mark task complete</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>Open task</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>1. Click 'Mark complete'</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>Status 'Completed'; badge count decreases.</t>
-        </is>
-      </c>
-      <c r="H138" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M138" s="5" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>TSK-004</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Tasks</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>Unauthorized user sees 'Access forbidden'</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>User not on case</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /cases/&lt;id&gt;/tasks</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr"/>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>'Access forbidden — You do not have permission to view tasks for this case.'</t>
-        </is>
-      </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>Needs account</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>TSK-005</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>Tasks</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Task comments</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>Existing task</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>1. Add comment</t>
-        </is>
-      </c>
       <c r="F140" s="5" t="inlineStr"/>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>Comment appears with date.</t>
-        </is>
-      </c>
-      <c r="H140" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Decisions recorded; source highlight shown.</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -9464,38 +9587,38 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>SEC-001</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>AI Read-In (Extraction)</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Site served over HTTPS</t>
+          <t>Paralegal cannot 'Confirm Approved Edits'</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Paralegal on case</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>1. Open http://34.232.246.13:3000</t>
+          <t>1. Try confirm</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr"/>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>App should be served over HTTPS; pilot currently uses plain HTTP (credentials in clear text) — finding.</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Blocked (403).</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
@@ -9505,55 +9628,51 @@
       </c>
       <c r="J141" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Paralegal</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L141" s="10" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="M141" s="5" t="inlineStr">
-        <is>
-          <t>BUG: pilot is served over plain http://34.232.246.13:3000 — passwords and tokens travel unencrypted.</t>
-        </is>
-      </c>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>SEC-002</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>AI Read-In (Extraction)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>API rejects requests without token</t>
+          <t>Clients cannot access extraction</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>1. Call a protected API (e.g. GET /api/v1/cases) without Authorization</t>
+          <t>1. Open extraction URL</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr"/>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>401.</t>
+          <t>403.</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -9568,70 +9687,66 @@
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="inlineStr">
-        <is>
-          <t>Automated — passed (2/2 runs)</t>
-        </is>
-      </c>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>SEC-003</t>
+          <t>TSK-001</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Cross-firm isolation via direct API</t>
+          <t>Case tasks page for staff</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Tokens for Firm A and B</t>
+          <t>Staff on case</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>1. Request Firm B case with Firm A token</t>
+          <t>1. Open /cases/&lt;id&gt;/tasks</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr"/>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>403/404, no data leak.</t>
-        </is>
-      </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Task list with due dates and status; open-task badge in navigation.</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
@@ -9649,33 +9764,33 @@
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>SEC-004</t>
+          <t>TSK-002</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>XSS in case name / names</t>
+          <t>Create task</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Staff on case</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>1. Create case named &lt;script&gt;alert(1)&lt;/script&gt;</t>
+          <t>1. Create task with title, description, due date, assignee</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr"/>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Rendered as text, no script execution.</t>
+          <t>Task listed as pending.</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
@@ -9685,12 +9800,12 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>Firm Admin</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
@@ -9708,53 +9823,53 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>SEC-005</t>
+          <t>TSK-003</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Brute-force on invitation tokens</t>
+          <t>Mark task complete</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Open task</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>1. Try many random tokens</t>
+          <t>1. Click 'Mark complete'</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr"/>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>No rate limiting today (documented gap) — record as risk.</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Status 'Completed'; badge count decreases.</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr">
@@ -9767,53 +9882,53 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>SEC-006</t>
+          <t>TSK-004</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Page load performance</t>
+          <t>Unauthorized user sees 'Access forbidden'</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>User not on case</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>1. Measure landing/login load</t>
+          <t>1. Open /cases/&lt;id&gt;/tasks</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr"/>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>Pages load within acceptable time (&lt; 3 s).</t>
-        </is>
-      </c>
-      <c r="H146" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>'Access forbidden — You do not have permission to view tasks for this case.'</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
@@ -9826,33 +9941,33 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>SEC-007</t>
+          <t>TSK-005</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Responsive layout on mobile width</t>
+          <t>Task comments</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Existing task</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>1. Open register/login at 375px width</t>
+          <t>1. Add comment</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr"/>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>No horizontal scroll; forms usable.</t>
+          <t>Comment appears with date.</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
@@ -9862,17 +9977,17 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
@@ -9885,7 +10000,7 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>SEC-008</t>
+          <t>SEC-001</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -9895,7 +10010,7 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Interactive API docs not publicly exposed</t>
+          <t>Site served over HTTPS</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -9905,50 +10020,471 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>1. Open http://34.232.246.13:8000/docs</t>
+          <t>1. Open http://34.232.246.13:3000</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr"/>
       <c r="G148" s="5" t="inlineStr">
         <is>
+          <t>App should be served over HTTPS; pilot currently uses plain HTTP (credentials in clear text) — finding.</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L148" s="10" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>BUG: pilot is served over plain http://34.232.246.13:3000 — passwords and tokens travel unencrypted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>SEC-002</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>API rejects requests without token</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>1. Call a protected API (e.g. GET /api/v1/cases) without Authorization</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>401.</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>Automated — passed (2/2 runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>SEC-003</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Cross-firm isolation via direct API</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Tokens for Firm A and B</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>1. Request Firm B case with Firm A token</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>403/404, no data leak.</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>SEC-004</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>XSS in case name / names</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>1. Create case named &lt;script&gt;alert(1)&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>Rendered as text, no script execution.</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>Firm Admin</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>Needs account</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>SEC-005</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Brute-force on invitation tokens</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>1. Try many random tokens</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>No rate limiting today (documented gap) — record as risk.</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>SEC-006</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Page load performance</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>1. Measure landing/login load</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr"/>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>Pages load within acceptable time (&lt; 3 s).</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>SEC-007</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Responsive layout on mobile width</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>1. Open register/login at 375px width</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>No horizontal scroll; forms usable.</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>SEC-008</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Non-functional</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Interactive API docs not publicly exposed</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>1. Open http://34.232.246.13:8000/docs</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr"/>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
           <t>Swagger/OpenAPI UI is not reachable on a pilot/production server (or is behind auth).</t>
         </is>
       </c>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="H155" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I148" s="5" t="inlineStr">
+      <c r="I155" s="5" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="J148" s="5" t="inlineStr">
+      <c r="J155" s="5" t="inlineStr">
         <is>
           <t>Guest</t>
         </is>
       </c>
-      <c r="K148" s="5" t="inlineStr">
+      <c r="K155" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L148" s="10" t="inlineStr">
+      <c r="L155" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="M148" s="5" t="inlineStr">
+      <c r="M155" s="5" t="inlineStr">
         <is>
           <t>BUG: http://34.232.246.13:8000/docs returns 200 — full Swagger UI of the API is public.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M148"/>
+  <autoFilter ref="A1:M155"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L148" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9962,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10882,7 +11418,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -10952,7 +11488,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11558,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11593,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11698,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11733,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11768,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11803,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11312,17 +11848,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASE-001</t>
+          <t>TEAM-013</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Case Management</t>
+          <t>Firm Team &amp; Staff Invitations</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Create case page layout</t>
+          <t>Invite success screen gives a usable invite link</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -11337,7 +11873,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11883,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASE-002</t>
+          <t>CASE-001</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11357,7 +11893,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Case name required</t>
+          <t>Create case page layout</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -11372,7 +11908,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11918,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CASE-003</t>
+          <t>CASE-002</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11392,7 +11928,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Case type required</t>
+          <t>Case name required</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11407,7 +11943,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11953,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CASE-004</t>
+          <t>CASE-003</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11427,7 +11963,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Case types are loaded</t>
+          <t>Case type required</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11442,7 +11978,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11988,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CASE-005</t>
+          <t>CASE-004</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11462,7 +11998,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Create case successfully</t>
+          <t>Case types are loaded</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11477,7 +12013,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11487,7 +12023,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASE-007</t>
+          <t>CASE-005</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11497,7 +12033,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Attorney/Paralegal cannot create case</t>
+          <t>Create case successfully</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -11512,7 +12048,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11522,7 +12058,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASE-008</t>
+          <t>CASE-007</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -11532,7 +12068,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Case list shows firm cases with status</t>
+          <t>Attorney/Paralegal cannot create case</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -11557,7 +12093,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASE-009</t>
+          <t>CASE-008</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11567,7 +12103,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Case detail page</t>
+          <t>Case list shows firm cases with status</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -11582,7 +12118,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11592,7 +12128,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASE-012</t>
+          <t>CASE-009</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11602,7 +12138,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Attorney sees only assigned cases' details</t>
+          <t>Case detail page</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -11617,7 +12153,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11627,7 +12163,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASE-013</t>
+          <t>CASE-012</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -11637,7 +12173,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Client sees only own case</t>
+          <t>Attorney sees only assigned cases' details</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -11662,17 +12198,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CTM-001</t>
+          <t>CASE-013</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Case Team</t>
+          <t>Case Management</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Empty draft case team message</t>
+          <t>Client sees only own case</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -11697,7 +12233,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CTM-002</t>
+          <t>CTM-001</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11707,7 +12243,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Invite beneficiary to case</t>
+          <t>Empty draft case team message</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -11722,7 +12258,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11732,7 +12268,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CTM-003</t>
+          <t>CTM-002</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11742,7 +12278,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Invite petitioner to case</t>
+          <t>Invite beneficiary to case</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -11757,7 +12293,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11767,7 +12303,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CTM-004</t>
+          <t>CTM-003</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -11777,7 +12313,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Invalid invitee email</t>
+          <t>Invite petitioner to case</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -11792,7 +12328,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11802,7 +12338,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CTM-005</t>
+          <t>CTM-004</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -11812,7 +12348,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Assign existing firm member (attorney/paralegal)</t>
+          <t>Invalid invitee email</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -11827,7 +12363,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11837,17 +12373,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QNR-001</t>
+          <t>CTM-005</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Questionnaires</t>
+          <t>Case Team</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Questionnaires tab with 'Add questionnaire'</t>
+          <t>Assign existing firm member (attorney/paralegal)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -11872,17 +12408,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QNR-002</t>
+          <t>CTM-010</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Questionnaires</t>
+          <t>Case Team</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Add questionnaire needs active beneficiary/petitioner</t>
+          <t>Pending invitee listed on case team page</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11897,7 +12433,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -11907,7 +12443,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QNR-003</t>
+          <t>QNR-001</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11917,7 +12453,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Attach published template to case</t>
+          <t>Questionnaires tab with 'Add questionnaire'</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11932,7 +12468,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11942,7 +12478,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QNR-004</t>
+          <t>QNR-002</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11952,7 +12488,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paralegal cannot attach questionnaire</t>
+          <t>Add questionnaire needs active beneficiary/petitioner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11967,7 +12503,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11977,7 +12513,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>QNR-005</t>
+          <t>QNR-003</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11987,7 +12523,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Client fills and autosaves answers</t>
+          <t>Attach published template to case</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -12012,7 +12548,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QNR-008</t>
+          <t>QNR-004</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12022,7 +12558,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Client submits questionnaire</t>
+          <t>Paralegal cannot attach questionnaire</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -12047,7 +12583,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>QNR-009</t>
+          <t>QNR-005</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12057,7 +12593,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Submit with missing required answers</t>
+          <t>Client fills and autosaves answers</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -12082,7 +12618,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>QNR-010</t>
+          <t>QNR-008</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12092,7 +12628,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Attorney requests changes</t>
+          <t>Client submits questionnaire</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -12117,7 +12653,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QNR-011</t>
+          <t>QNR-009</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12127,7 +12663,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Attorney approves</t>
+          <t>Submit with missing required answers</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -12152,7 +12688,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>QNR-012</t>
+          <t>QNR-010</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12162,7 +12698,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paralegal cannot approve / export / archive</t>
+          <t>Attorney requests changes</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -12187,7 +12723,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QNR-014</t>
+          <t>QNR-011</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12197,7 +12733,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Client-visible vs internal comments</t>
+          <t>Attorney approves</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -12222,17 +12758,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOC-001</t>
+          <t>QNR-012</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Questionnaires</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Documents page gated until questionnaire exists</t>
+          <t>Paralegal cannot approve / export / archive</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -12257,17 +12793,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOC-002</t>
+          <t>QNR-014</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Questionnaires</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Required documents checklist</t>
+          <t>Client-visible vs internal comments</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -12292,7 +12828,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DOC-003</t>
+          <t>DOC-001</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12302,7 +12838,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Upload valid PDF</t>
+          <t>Documents page gated until questionnaire exists</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -12317,7 +12853,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12863,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DOC-005</t>
+          <t>DOC-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12337,7 +12873,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Reject unsupported file type</t>
+          <t>Required documents checklist</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -12362,7 +12898,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DOC-006</t>
+          <t>DOC-003</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12372,7 +12908,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Reject file over 25 MB</t>
+          <t>Upload valid PDF</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -12397,7 +12933,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DOC-010</t>
+          <t>DOC-005</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12407,7 +12943,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Client cannot see other cases' documents</t>
+          <t>Reject unsupported file type</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -12432,17 +12968,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>DOC-006</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AI Read-In (Extraction)</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Clients cannot access extraction</t>
+          <t>Reject file over 25 MB</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -12467,17 +13003,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TSK-004</t>
+          <t>DOC-010</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Unauthorized user sees 'Access forbidden'</t>
+          <t>Client cannot see other cases' documents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -12502,17 +13038,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEC-003</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Security &amp; Non-functional</t>
+          <t>AI Read-In (Extraction)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cross-firm isolation via direct API</t>
+          <t>Clients cannot access extraction</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -12537,27 +13073,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>REG-007</t>
+          <t>TSK-004</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Registration (Firm Admin)</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Successful registration sends OTP</t>
+          <t>Unauthorized user sees 'Access forbidden'</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Needs mailbox</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>needs mailbox access</t>
+          <t>needs test accounts</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -12572,27 +13108,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>REG-012</t>
+          <t>SEC-003</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Registration (Firm Admin)</t>
+          <t>Security &amp; Non-functional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Invite link pre-fills and locks email</t>
+          <t>Cross-firm isolation via direct API</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Needs mailbox</t>
+          <t>Needs account</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>needs mailbox access</t>
+          <t>needs test accounts</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -12607,7 +13143,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>REG-013</t>
+          <t>REG-007</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12617,7 +13153,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Firm auto-created from email domain after confirmation</t>
+          <t>Successful registration sends OTP</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12642,17 +13178,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OTP-005</t>
+          <t>REG-012</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Email Verification (OTP)</t>
+          <t>Registration (Firm Admin)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wrong code</t>
+          <t>Invite link pre-fills and locks email</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12677,17 +13213,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OTP-006</t>
+          <t>REG-013</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Email Verification (OTP)</t>
+          <t>Registration (Firm Admin)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Correct code confirms account</t>
+          <t>Firm auto-created from email domain after confirmation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12712,17 +13248,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FPW-004</t>
+          <t>OTP-005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Email Verification (OTP)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Reset code sent for registered email</t>
+          <t>Wrong code</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -12747,17 +13283,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FPW-007</t>
+          <t>OTP-006</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Forgot Password</t>
+          <t>Email Verification (OTP)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Successful reset then login with new password</t>
+          <t>Correct code confirms account</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12782,17 +13318,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INV-003</t>
+          <t>FPW-004</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Invitation Accept</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Used or expired token</t>
+          <t>Reset code sent for registered email</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -12817,17 +13353,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INV-004</t>
+          <t>FPW-007</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Invitation Accept</t>
+          <t>Forgot Password</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>New user accepts via sign-up</t>
+          <t>Successful reset then login with new password</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12852,7 +13388,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INV-005</t>
+          <t>INV-003</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12862,7 +13398,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Existing user accepts after login</t>
+          <t>Used or expired token</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12887,7 +13423,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INV-007</t>
+          <t>INV-004</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -12897,7 +13433,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>First accepted client invite activates draft case</t>
+          <t>New user accepts via sign-up</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12922,7 +13458,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INV-010</t>
+          <t>INV-005</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12932,7 +13468,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Token can be used only once</t>
+          <t>Existing user accepts after login</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12957,30 +13493,100 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>INV-007</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Invitation Accept</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>First accepted client invite activates draft case</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Needs mailbox</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>needs mailbox access</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>INV-010</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Invitation Accept</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Token can be used only once</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Needs mailbox</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>needs mailbox access</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>CTM-009</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Case Team</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Case status flips to active after first acceptance</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Needs mailbox</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>needs mailbox access</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
